--- a/ДП/Ресурсы/Экономическая часть.xlsx
+++ b/ДП/Ресурсы/Экономическая часть.xlsx
@@ -5,19 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slavv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\Projects\ДП\Ресурсы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA6A3A9-C47C-426F-A44F-328DBA271DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBE6731-92EA-41A1-AF64-907A0B178E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4B5BF2D2-6468-494A-A058-D8821C81D191}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B5BF2D2-6468-494A-A058-D8821C81D191}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>Зспп</t>
   </si>
@@ -77,9 +74,6 @@
     <t>tот</t>
   </si>
   <si>
-    <t>tAот</t>
-  </si>
-  <si>
     <t>tд</t>
   </si>
   <si>
@@ -90,9 +84,6 @@
   </si>
   <si>
     <t>tдо</t>
-  </si>
-  <si>
-    <t>Дни (8/день)</t>
   </si>
   <si>
     <t>Зобщ</t>
@@ -123,9 +114,6 @@
   </si>
   <si>
     <t>Рэвм</t>
-  </si>
-  <si>
-    <t>Сэвм</t>
   </si>
   <si>
     <t>За</t>
@@ -166,6 +154,57 @@
   <si>
     <t>издержки на заработную плату</t>
   </si>
+  <si>
+    <t>Сэл</t>
+  </si>
+  <si>
+    <t>затраты труда на разработку алгоритма решения задачи</t>
+  </si>
+  <si>
+    <t>затраты труда на изучение описания задачи</t>
+  </si>
+  <si>
+    <t>затраты труда на отладку</t>
+  </si>
+  <si>
+    <t>затраты труда на подготовку документации</t>
+  </si>
+  <si>
+    <t>затраты времени на составление программы по готовой диаграмме</t>
+  </si>
+  <si>
+    <t>затраты труда на разработку блок-схемы алгоритма решения задачи</t>
+  </si>
+  <si>
+    <t>Ззп Ф</t>
+  </si>
+  <si>
+    <t>Переменные</t>
+  </si>
+  <si>
+    <t>KдФ</t>
+  </si>
+  <si>
+    <t>КдС</t>
+  </si>
+  <si>
+    <t>Трудозатраты</t>
+  </si>
+  <si>
+    <t>Затраты на электоэнергию</t>
+  </si>
+  <si>
+    <t>Для Q</t>
+  </si>
+  <si>
+    <t>Затраты на ЗП и далее</t>
+  </si>
+  <si>
+    <t>tотл</t>
+  </si>
+  <si>
+    <t>tAотл</t>
+  </si>
 </sst>
 </file>
 
@@ -199,7 +238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,24 +265,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -337,11 +370,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,15 +430,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -375,37 +441,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,7 +901,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Лист1!$B$21:$B$24</c:f>
+              <c:f>Лист1!$C$26:$C$29</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -807,7 +921,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$C$21:$C$24</c:f>
+              <c:f>Лист1!$D$27:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -896,7 +1010,810 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.28954387887003336"/>
+          <c:y val="0.16219525530985918"/>
+          <c:w val="0.48072165146539186"/>
+          <c:h val="0.67898855719923701"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D8ED-413A-8BAB-17EF08D35434}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D8ED-413A-8BAB-17EF08D35434}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-D8ED-413A-8BAB-17EF08D35434}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-D8ED-413A-8BAB-17EF08D35434}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-D8ED-413A-8BAB-17EF08D35434}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-D8ED-413A-8BAB-17EF08D35434}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.13906307689412692"/>
+                  <c:y val="-0.19620009522555298"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:xfrm>
+                  <a:off x="4520712" y="389563"/>
+                  <a:ext cx="1252025" cy="600421"/>
+                </a:xfrm>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator> </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val -98845"/>
+                        <a:gd name="adj2" fmla="val 107241"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.17014033309562726"/>
+                      <c:h val="0.1520622916941031"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-D8ED-413A-8BAB-17EF08D35434}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.2708609782891541E-2"/>
+                  <c:y val="-0.13187219515160112"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator> </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val -123013"/>
+                        <a:gd name="adj2" fmla="val 14679"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-D8ED-413A-8BAB-17EF08D35434}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.7083443913156627E-2"/>
+                  <c:y val="-2.5731160029580705E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator> </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val -141640"/>
+                        <a:gd name="adj2" fmla="val -92856"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-D8ED-413A-8BAB-17EF08D35434}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.10919014041096113"/>
+                  <c:y val="6.5019298370022184E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator> </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val 148602"/>
+                        <a:gd name="adj2" fmla="val -115864"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-D8ED-413A-8BAB-17EF08D35434}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.10300956642543517"/>
+                  <c:y val="-9.6491850110927788E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator> </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val 169276"/>
+                        <a:gd name="adj2" fmla="val 76189"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-D8ED-413A-8BAB-17EF08D35434}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="5.5625165869734761E-2"/>
+                  <c:y val="-8.3626270096137351E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ru-RU"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator> </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val 99866"/>
+                        <a:gd name="adj2" fmla="val 64441"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-D8ED-413A-8BAB-17EF08D35434}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12700">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$C$32:$C$37</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>затраты труда на изучение описания задачи</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>затраты труда на разработку алгоритма решения задачи</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>затраты труда на разработку блок-схемы алгоритма решения задачи</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>затраты времени на составление программы по готовой диаграмме</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>затраты труда на отладку</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>затраты труда на подготовку документации</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$D$33:$D$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18.525176470588239</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.552000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.552000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.328000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.664000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-D8ED-413A-8BAB-17EF08D35434}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="101"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent4"/>
@@ -1447,13 +2364,527 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="254">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>87580</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>73851</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="563424" cy="125227"/>
@@ -1514,9 +2945,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>84715</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>33340</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="722890" cy="248658"/>
@@ -1804,9 +3235,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>94742</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>17883</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="715259" cy="248658"/>
@@ -2053,9 +3484,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>99756</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>33419</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="721159" cy="248658"/>
@@ -2302,9 +3733,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>101371</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>95861</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="671401" cy="132024"/>
@@ -2574,9 +4005,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>93200</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>33738</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="734175" cy="248658"/>
@@ -2944,9 +4375,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>102191</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>88003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="634083" cy="134268"/>
@@ -3224,9 +4655,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>82519</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>14111</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="853247" cy="248658"/>
@@ -3484,9 +4915,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>90065</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>81754</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="737189" cy="134268"/>
@@ -3777,9 +5208,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>145329</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>33010</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1844479" cy="173766"/>
@@ -3939,9 +5370,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>141984</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>50175</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1056058" cy="173766"/>
@@ -4138,9 +5569,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>124723</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>63235</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1181477" cy="185500"/>
@@ -4392,9 +5823,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>103694</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="706668" cy="346505"/>
@@ -4631,9 +6062,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>125507</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>85035</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2152128" cy="184409"/>
@@ -4926,9 +6357,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>112365</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>94290</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="967381" cy="173766"/>
@@ -5172,9 +6603,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>101382</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>60769</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1660455" cy="184409"/>
@@ -5428,9 +6859,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>101067</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>90766</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1267398" cy="179152"/>
@@ -5711,9 +7142,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>92498</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>294592</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2109552" cy="322461"/>
@@ -5844,7 +7275,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5858,7 +7289,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -5871,7 +7302,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -5885,7 +7316,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -5899,7 +7330,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5913,7 +7344,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -5926,7 +7357,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -6089,23 +7520,11 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                   <a:effectLst/>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:rPr>
-                <a:t>+З_св+З_</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:effectLst/>
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:rPr>
-                <a:t>эл+З_ам</a:t>
+                <a:t>+З_св+З_эл+З_ам</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
@@ -6136,9 +7555,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>84412</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>96790</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1811586" cy="184409"/>
@@ -6408,9 +7827,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>109822</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>57617</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1142620" cy="185948"/>
@@ -6626,16 +8045,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>8441</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>239523</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>523912</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>172288</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>554873</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>311782</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>285932</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>244547</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6660,60 +8079,45 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>491596</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>68697</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>297465</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>142904</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B07D8FB-1530-4547-90E4-65F0463E0897}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Задание 1"/>
-      <sheetName val="Задание 2"/>
-      <sheetName val="Задание 3"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="21">
-          <cell r="D21" t="str">
-            <v>техзадание</v>
-          </cell>
-          <cell r="E21">
-            <v>45.924705882352939</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="D22" t="str">
-            <v>техпроект</v>
-          </cell>
-          <cell r="E22">
-            <v>22.560000000000002</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="D23" t="str">
-            <v>рабочий проект</v>
-          </cell>
-          <cell r="E23">
-            <v>49.632000000000005</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="D24" t="str">
-            <v>внедрение</v>
-          </cell>
-          <cell r="E24">
-            <v>16.920000000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7033,405 +8437,624 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8165C76F-C09E-4153-BB20-3B1B98EC2564}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultRowHeight="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="20" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="9" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="7" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="12.42578125" customWidth="1"/>
+    <col min="23" max="23" width="21.140625" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="E1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="29"/>
+      <c r="H1" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="L1" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="Q1" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+    </row>
+    <row r="2" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7">
+      <c r="C2" s="19">
         <v>540</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="19">
+        <f>ROUND(C2*C3*(1+C5),2)</f>
+        <v>933.12</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="31">
+        <v>30</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="L2" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="33">
+        <f>ROUND(M3*M4,2)</f>
+        <v>22.75</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="17">
-        <f>F2*F3</f>
-        <v>22.866105600000001</v>
-      </c>
-      <c r="J1" s="18" t="s">
+      <c r="R2" s="23">
+        <f>ROUND(C12*(1+C13+C14),2)</f>
+        <v>46058.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37"/>
+      <c r="B3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19">
+        <v>1.08</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="19">
+        <f>ROUND((E2*C4)/(85*C6),2)</f>
+        <v>18.53</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="L3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="23">
+        <f>ROUND(M6/M5,2)</f>
+        <v>0.45</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="23">
+        <f>ROUND(R2/C15*I12,2)</f>
+        <v>32898.639999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="37"/>
+      <c r="B4" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="20">
+        <v>1.35</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="19">
+        <f>ROUND(E2/(75*C6),2)</f>
+        <v>15.55</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="L4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="19">
+        <f>ROUND(I5+I6+I8,2)</f>
+        <v>50.55</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" s="23">
+        <f>ROUND(R3*30/100,2)</f>
+        <v>9869.59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="37"/>
+      <c r="B5" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="19">
+        <f>ROUND(E2/(75*C6),2)</f>
+        <v>15.55</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="L5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="20">
+        <f>8*(C8-C9)-C10*4</f>
+        <v>128</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5" s="23">
         <v>0</v>
       </c>
-      <c r="K1" s="19">
-        <f>F1+F20</f>
-        <v>66615.574105599997</v>
-      </c>
-      <c r="M1" s="20"/>
     </row>
-    <row r="2" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1.08</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="25">
-        <f>F8/F4</f>
-        <v>0.45239999999999997</v>
+    <row r="6" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="19">
+        <f>ROUND(1.5*I7,2)</f>
+        <v>23.33</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="L6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="23">
+        <f>ROUND(M8+M7,2)</f>
+        <v>57.91</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="23">
+        <f>ROUND(((R3+R4+M7+R5)*10)/90,2)</f>
+        <v>4758.46</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="7" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="19">
+        <f>ROUND(E2/(75*C6),2)</f>
+        <v>15.55</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="L7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="19">
+        <f>ROUND(C16*M5*C17,2)</f>
+        <v>57.91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="20">
+        <v>28</v>
+      </c>
+      <c r="G8" s="25"/>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="19">
+        <f>ROUND(I9+I10,2)</f>
+        <v>11.67</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="L8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36"/>
+      <c r="B9" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="20">
         <v>10</v>
       </c>
-      <c r="B3" s="6">
-        <v>1.35</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="G9" s="25"/>
+      <c r="H9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="19">
+        <f>ROUND(E2/(175*C6),2)</f>
+        <v>6.67</v>
+      </c>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:19" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="36"/>
+      <c r="B10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="20">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="19">
+        <f>ROUND(0.75*I9,2)</f>
+        <v>5</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="L10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="23">
+        <f>ROUND(R3+R4+R5+M7+R6,2)</f>
+        <v>47584.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="19">
+        <f>ROUND(I8+I6+I3+I4+I5+I2,2)</f>
+        <v>114.63</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="M11" s="38">
+        <f>ROUND(M2+M10,2)</f>
+        <v>47607.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="23">
+        <v>27093</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="21">
+        <f>ROUNDUP(J12,0)</f>
+        <v>15</v>
+      </c>
+      <c r="J12" s="22">
+        <f>I11/8</f>
+        <v>14.328749999999999</v>
+      </c>
+      <c r="K12" s="25"/>
+    </row>
+    <row r="13" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36"/>
+      <c r="B14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="25"/>
+    </row>
+    <row r="15" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36"/>
+      <c r="B15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36"/>
+      <c r="B16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7">
-        <f>B11+B13+B16</f>
-        <v>50.544000000000004</v>
+      <c r="C16" s="20">
+        <v>0.06</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="6">
-        <f>8*(F5-F6)-F7*4</f>
-        <v>128</v>
-      </c>
+    <row r="17" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36"/>
+      <c r="B17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="20">
+        <v>7.54</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
     </row>
-    <row r="5" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="E5" s="1" t="s">
+    <row r="18" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="26" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="6">
-        <v>28</v>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27">
+        <v>665.92</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="6">
-        <v>10</v>
-      </c>
+    <row r="28" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28">
+        <v>46058.1</v>
+      </c>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
     </row>
-    <row r="7" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7">
-        <f>B1*B2*(1+B4)</f>
-        <v>933.12000000000012</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="E7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="6">
-        <v>4</v>
+    <row r="29" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29">
+        <v>13817.43</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="30" spans="1:25" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30">
+        <v>6659.1683999999996</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+    </row>
+    <row r="31" spans="1:25" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="14">
+        <f>M11</f>
+        <v>47607.35</v>
+      </c>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+    </row>
+    <row r="32" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="Y32" s="14"/>
+    </row>
+    <row r="33" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="17">
         <v>30</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="25">
-        <f>F9+F10</f>
-        <v>57.907199999999996</v>
-      </c>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
     </row>
-    <row r="9" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="34" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
-        <f>(B7*B3)/(85*B5)</f>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="17">
         <v>18.525176470588239</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="E9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
     </row>
-    <row r="10" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="35" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
-        <f>B7/(75*B5)</f>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="17">
         <v>15.552000000000001</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="E10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="7">
-        <f>F11*F4*F12</f>
-        <v>57.907199999999996</v>
-      </c>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
     </row>
-    <row r="11" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="36" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
-        <f>B7/(75*B5)</f>
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="17">
         <v>15.552000000000001</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="E11" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.06</v>
-      </c>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
     </row>
-    <row r="12" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="37" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="17">
+        <v>23.328000000000003</v>
+      </c>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+    </row>
+    <row r="38" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7">
-        <f>B7/(75*B5)</f>
-        <v>15.552000000000001</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="E12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="6">
-        <v>7.54</v>
+      <c r="D38" s="17">
+        <v>11.664000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="7">
-        <f>1.5*B12</f>
-        <v>23.328000000000003</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="E13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="25">
-        <f>F14*(1+F15+F16)</f>
-        <v>46058.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="7">
-        <f>B7/(175*B5)</f>
-        <v>6.6651428571428584</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="E14" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="25">
-        <v>27093</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="7">
-        <f>0.75*B14</f>
-        <v>4.998857142857144</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="E15" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7">
-        <f>B14+B15</f>
-        <v>11.664000000000001</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="E16" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7">
-        <f>B16+B13+B9+B10+B11+B8</f>
-        <v>114.62117647058825</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="E17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="25">
-        <f>F13*30/100</f>
-        <v>13817.43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6">
-        <f>ROUND(B17/8,0)</f>
-        <v>14</v>
-      </c>
-      <c r="C18" s="5">
-        <f>B17/8</f>
-        <v>14.327647058823532</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="25">
-        <f>((F13+F17+F10+F18)*10)/90</f>
-        <v>6659.2707999999993</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="25">
-        <f>F13+F17+F18+F10+F19</f>
-        <v>66592.707999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21">
-        <v>665.92</v>
-      </c>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22">
-        <v>46058.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23">
-        <v>13817.43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24">
-        <v>6659.1683999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="22">
-        <f>K1</f>
-        <v>66615.574105599997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J31" s="22"/>
-    </row>
-    <row r="35" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="13"/>
-    </row>
-    <row r="39" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="O39" s="4"/>
     </row>
-    <row r="41" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="4"/>
+    <row r="40" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
     </row>
-    <row r="43" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
+    <row r="41" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
   <drawing r:id="rId2"/>
